--- a/output/reports/cv_experiment_Bagging_qcut_regression.xlsx
+++ b/output/reports/cv_experiment_Bagging_qcut_regression.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>6.274673461914062</v>
+        <v>1.399111270904541</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9999952989031139</v>
+        <v>0.9916308390247451</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9999980186895508</v>
+        <v>0.9922108407265826</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2504775645776107</v>
+        <v>1.739219543134441</v>
       </c>
       <c r="H2" t="n">
-        <v>0.02845799769850308</v>
+        <v>1.121023376623376</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 50, 'max_samples': 1.0, 'max_features': 1.0}</t>
+          <t>{'n_estimators': 50, 'max_samples': 0.8, 'max_features': 1.0}</t>
         </is>
       </c>
     </row>
@@ -526,93 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>11.89019393920898</v>
+        <v>1.957748651504517</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9999976282896125</v>
+        <v>0.991944820007945</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9999980186895508</v>
+        <v>0.9924359336701404</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2504775645776107</v>
+        <v>1.713905130730069</v>
       </c>
       <c r="H3" t="n">
-        <v>0.02845799769850308</v>
+        <v>1.105564935064935</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 50, 'max_samples': 1.0, 'max_features': 1.0}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Bagging</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>25.70109081268311</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9999979939925131</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.999997797671765</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.264078831902803</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.0301841196777909</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'n_estimators': 25, 'max_samples': 1.0, 'max_features': 1.0}</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Bagging</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>15</v>
-      </c>
-      <c r="D5" t="n">
-        <v>39.7575249671936</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.9999979563094777</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.9999980186895508</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0.2504775645776107</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.02845799769850308</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>{'n_estimators': 50, 'max_samples': 1.0, 'max_features': 1.0}</t>
+          <t>{'n_estimators': 100, 'max_samples': 0.8, 'max_features': 1.0}</t>
         </is>
       </c>
     </row>
@@ -627,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -692,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>6.274673461914062</v>
+        <v>1.399111270904541</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9999952989031139</v>
+        <v>0.9916308390247451</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9999980186895508</v>
+        <v>0.9922108407265826</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2504775645776107</v>
+        <v>1.739219543134441</v>
       </c>
       <c r="H2" t="n">
-        <v>0.02845799769850308</v>
+        <v>1.121023376623376</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 50, 'max_samples': 1.0, 'max_features': 1.0}</t>
+          <t>{'n_estimators': 50, 'max_samples': 0.8, 'max_features': 1.0}</t>
         </is>
       </c>
     </row>
@@ -727,93 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>11.89019393920898</v>
+        <v>1.957748651504517</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9999976282896125</v>
+        <v>0.991944820007945</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9999980186895508</v>
+        <v>0.9924359336701404</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2504775645776107</v>
+        <v>1.713905130730069</v>
       </c>
       <c r="H3" t="n">
-        <v>0.02845799769850308</v>
+        <v>1.105564935064935</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 50, 'max_samples': 1.0, 'max_features': 1.0}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Bagging</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>25.70109081268311</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9999979939925131</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.999997797671765</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.264078831902803</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.0301841196777909</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'n_estimators': 25, 'max_samples': 1.0, 'max_features': 1.0}</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Bagging</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>15</v>
-      </c>
-      <c r="D5" t="n">
-        <v>39.7575249671936</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.9999979563094777</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.9999980186895508</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0.2504775645776107</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.02845799769850308</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>{'n_estimators': 50, 'max_samples': 1.0, 'max_features': 1.0}</t>
+          <t>{'n_estimators': 100, 'max_samples': 0.8, 'max_features': 1.0}</t>
         </is>
       </c>
     </row>
